--- a/GameDesign/Excel/Industry.xlsx
+++ b/GameDesign/Excel/Industry.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="2"/>
@@ -446,9 +446,10 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -485,15 +486,20 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>판정 1회당 캐릭터 경험치</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>해금: 산업 적성 요구치</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>해금: 계정 레벨 요구치</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>설명 (메모 — 로직 미사용)</t>
         </is>
@@ -545,6 +551,11 @@
           <t>a</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -588,6 +599,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -614,7 +630,10 @@
       <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="n"/>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -629,11 +648,12 @@
       </c>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -648,7 +668,8 @@
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -683,15 +704,20 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>ExpPerJudge</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>RequiredAptitude</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>RequiredAccountLevel</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -718,12 +744,15 @@
         <v>30000</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
@@ -753,9 +782,12 @@
         <v>3</v>
       </c>
       <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
         <v>5</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -782,12 +814,15 @@
         <v>270000</v>
       </c>
       <c r="G11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" t="n">
         <v>5</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>15</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -814,12 +849,15 @@
         <v>810000</v>
       </c>
       <c r="G12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H12" t="n">
         <v>7</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>30</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -846,12 +884,15 @@
         <v>2430000</v>
       </c>
       <c r="G13" t="n">
+        <v>81</v>
+      </c>
+      <c r="H13" t="n">
         <v>9</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>50</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -878,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="2"/>
@@ -886,9 +927,10 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -925,15 +967,20 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>판정 1회당 캐릭터 경험치</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>해금: 산업 적성 요구치</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>해금: 계정 레벨 요구치</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>설명 (메모 — 로직 미사용)</t>
         </is>
@@ -985,6 +1032,11 @@
           <t>a</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1028,6 +1080,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1054,7 +1111,10 @@
       <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="n"/>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1069,11 +1129,12 @@
       </c>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1088,7 +1149,8 @@
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -1123,15 +1185,20 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>ExpPerJudge</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>RequiredAptitude</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>RequiredAccountLevel</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -1158,12 +1225,15 @@
         <v>30000</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
@@ -1193,9 +1263,12 @@
         <v>3</v>
       </c>
       <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
         <v>5</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -1222,12 +1295,15 @@
         <v>270000</v>
       </c>
       <c r="G11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" t="n">
         <v>5</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>15</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -1254,12 +1330,15 @@
         <v>810000</v>
       </c>
       <c r="G12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H12" t="n">
         <v>7</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>30</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -1286,12 +1365,15 @@
         <v>2430000</v>
       </c>
       <c r="G13" t="n">
+        <v>81</v>
+      </c>
+      <c r="H13" t="n">
         <v>9</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>50</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -1318,7 +1400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="2"/>
@@ -1326,9 +1408,10 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -1365,15 +1448,20 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>판정 1회당 캐릭터 경험치</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>해금: 산업 적성 요구치</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>해금: 계정 레벨 요구치</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>설명 (메모 — 로직 미사용)</t>
         </is>
@@ -1425,6 +1513,11 @@
           <t>a</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1468,6 +1561,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1494,7 +1592,10 @@
       <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="n"/>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1509,11 +1610,12 @@
       </c>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1528,7 +1630,8 @@
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -1563,15 +1666,20 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>ExpPerJudge</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>RequiredAptitude</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>RequiredAccountLevel</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -1598,12 +1706,15 @@
         <v>30000</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
@@ -1633,9 +1744,12 @@
         <v>3</v>
       </c>
       <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
         <v>5</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -1662,12 +1776,15 @@
         <v>270000</v>
       </c>
       <c r="G11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" t="n">
         <v>5</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>15</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -1694,12 +1811,15 @@
         <v>810000</v>
       </c>
       <c r="G12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H12" t="n">
         <v>7</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>30</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -1726,12 +1846,15 @@
         <v>2430000</v>
       </c>
       <c r="G13" t="n">
+        <v>81</v>
+      </c>
+      <c r="H13" t="n">
         <v>9</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>50</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -1758,7 +1881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="2"/>
@@ -1766,9 +1889,10 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -1805,15 +1929,20 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>판정 1회당 캐릭터 경험치</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>해금: 산업 적성 요구치</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>해금: 계정 레벨 요구치</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>설명 (메모 — 로직 미사용)</t>
         </is>
@@ -1865,6 +1994,11 @@
           <t>a</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1908,6 +2042,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1934,7 +2073,10 @@
       <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="n"/>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,11 +2091,12 @@
       </c>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1968,7 +2111,8 @@
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -2003,15 +2147,20 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>ExpPerJudge</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>RequiredAptitude</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>RequiredAccountLevel</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -2038,12 +2187,15 @@
         <v>30000</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
@@ -2073,9 +2225,12 @@
         <v>3</v>
       </c>
       <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
         <v>5</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -2102,12 +2257,15 @@
         <v>270000</v>
       </c>
       <c r="G11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" t="n">
         <v>5</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>15</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -2134,12 +2292,15 @@
         <v>810000</v>
       </c>
       <c r="G12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H12" t="n">
         <v>7</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>30</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -2166,12 +2327,15 @@
         <v>2430000</v>
       </c>
       <c r="G13" t="n">
+        <v>81</v>
+      </c>
+      <c r="H13" t="n">
         <v>9</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>50</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -2198,7 +2362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="2"/>
@@ -2206,9 +2370,10 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -2245,15 +2410,20 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>판정 1회당 캐릭터 경험치</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>해금: 산업 적성 요구치</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>해금: 계정 레벨 요구치</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>설명 (메모 — 로직 미사용)</t>
         </is>
@@ -2305,6 +2475,11 @@
           <t>a</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2348,6 +2523,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -2374,7 +2554,10 @@
       <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="n"/>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2389,11 +2572,12 @@
       </c>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2408,7 +2592,8 @@
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -2443,15 +2628,20 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>ExpPerJudge</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>RequiredAptitude</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>RequiredAccountLevel</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -2478,12 +2668,15 @@
         <v>30000</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
@@ -2513,9 +2706,12 @@
         <v>3</v>
       </c>
       <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
         <v>5</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -2542,12 +2738,15 @@
         <v>270000</v>
       </c>
       <c r="G11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" t="n">
         <v>5</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>15</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -2574,12 +2773,15 @@
         <v>810000</v>
       </c>
       <c r="G12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H12" t="n">
         <v>7</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>30</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -2606,12 +2808,15 @@
         <v>2430000</v>
       </c>
       <c r="G13" t="n">
+        <v>81</v>
+      </c>
+      <c r="H13" t="n">
         <v>9</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>50</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>

--- a/GameDesign/Excel/Industry.xlsx
+++ b/GameDesign/Excel/Industry.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,8 +39,16 @@
       <sz val="11"/>
       <vertAlign val="baseline"/>
     </font>
+    <font/>
+    <font>
+      <color theme="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color theme="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -52,8 +60,13 @@
         <fgColor rgb="00DDDDDD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -61,17 +74,61 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -147,6 +204,156 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>판정 1회 필요 점수 (적성1 = 1000점/초)</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>판정 1회당 캐릭터 경험치</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>해금: 산업 적성 요구치</t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>해금: 계정 레벨 요구치</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>판정 1회 필요 점수 (적성1 = 1000점/초)</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>판정 1회당 캐릭터 경험치</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>해금: 산업 적성 요구치</t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>해금: 계정 레벨 요구치</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>판정 1회 필요 점수 (적성1 = 1000점/초)</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>판정 1회당 캐릭터 경험치</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>해금: 산업 적성 요구치</t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>해금: 계정 레벨 요구치</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>판정 1회 필요 점수 (적성1 = 1000점/초)</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>판정 1회당 캐릭터 경험치</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>해금: 산업 적성 요구치</t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>해금: 계정 레벨 요구치</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>판정 1회 필요 점수 (적성1 = 1000점/초)</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>판정 1회당 캐릭터 경험치</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>해금: 산업 적성 요구치</t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>해금: 계정 레벨 요구치</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -433,7 +640,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -441,235 +648,236 @@
   <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="1" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>산업 레벨 TID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>산업 종류</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>레벨</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>판정 1회 필요 점수 (적성1 = 1000점/초)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>판정 1회당 캐릭터 경험치</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>해금: 산업 적성 요구치</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>해금: 계정 레벨 요구치</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>설명 (메모 — 로직 미사용)</t>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>판정 점수</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>판정 경험치</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>요구 적성</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>요구 계정 Lv</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>eIndustryType</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n">
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n">
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="2" t="n"/>
+      <c r="J5" s="11" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n">
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n">
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -677,222 +885,222 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>IndustryLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>IndustryType</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>RequiredScore</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>ExpPerJudge</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>RequiredAptitude</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>RequiredAccountLevel</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
+      <c r="B9" s="7" t="n">
         <v>101</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>텃밭</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>30000</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
+      <c r="B10" s="7" t="n">
         <v>102</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>밭</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>90000</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
+      <c r="B11" s="7" t="n">
         <v>103</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>농장</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>270000</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
+      <c r="B12" s="7" t="n">
         <v>104</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>대농장</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>810000</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
+      <c r="B13" s="7" t="n">
         <v>105</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>신성한 대지</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="7" t="n">
         <v>2430000</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -910,11 +1118,12 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -922,235 +1131,236 @@
   <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="1" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>산업 레벨 TID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>산업 종류</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>레벨</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>판정 1회 필요 점수 (적성1 = 1000점/초)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>판정 1회당 캐릭터 경험치</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>해금: 산업 적성 요구치</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>해금: 계정 레벨 요구치</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>설명 (메모 — 로직 미사용)</t>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>판정 점수</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>판정 경험치</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>요구 적성</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>요구 계정 Lv</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>eIndustryType</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n">
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n">
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="2" t="n"/>
+      <c r="J5" s="11" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n">
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n">
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -1158,222 +1368,222 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>IndustryLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>IndustryType</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>RequiredScore</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>ExpPerJudge</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>RequiredAptitude</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>RequiredAccountLevel</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
+      <c r="B9" s="7" t="n">
         <v>201</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>개울</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>30000</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
+      <c r="B10" s="7" t="n">
         <v>202</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>저수지</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>90000</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
+      <c r="B11" s="7" t="n">
         <v>203</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>강 하류</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>270000</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
+      <c r="B12" s="7" t="n">
         <v>204</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>호수</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>810000</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
+      <c r="B13" s="7" t="n">
         <v>205</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>심해</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="7" t="n">
         <v>2430000</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -1391,11 +1601,12 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1403,235 +1614,236 @@
   <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="1" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>산업 레벨 TID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>산업 종류</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>레벨</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>판정 1회 필요 점수 (적성1 = 1000점/초)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>판정 1회당 캐릭터 경험치</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>해금: 산업 적성 요구치</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>해금: 계정 레벨 요구치</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>설명 (메모 — 로직 미사용)</t>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>판정 점수</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>판정 경험치</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>요구 적성</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>요구 계정 Lv</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>eIndustryType</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n">
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n">
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="2" t="n"/>
+      <c r="J5" s="11" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n">
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n">
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -1639,222 +1851,222 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>IndustryLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>IndustryType</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>RequiredScore</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>ExpPerJudge</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>RequiredAptitude</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>RequiredAccountLevel</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
+      <c r="B9" s="7" t="n">
         <v>301</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>노천 광산</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>30000</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
+      <c r="B10" s="7" t="n">
         <v>302</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>갱도</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>90000</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
+      <c r="B11" s="7" t="n">
         <v>303</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>심층 갱도</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>270000</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
+      <c r="B12" s="7" t="n">
         <v>304</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>지하 대공동</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>810000</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
+      <c r="B13" s="7" t="n">
         <v>305</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>심연</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="7" t="n">
         <v>2430000</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -1872,11 +2084,12 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1884,235 +2097,236 @@
   <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="1" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>산업 레벨 TID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>산업 종류</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>레벨</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>판정 1회 필요 점수 (적성1 = 1000점/초)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>판정 1회당 캐릭터 경험치</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>해금: 산업 적성 요구치</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>해금: 계정 레벨 요구치</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>설명 (메모 — 로직 미사용)</t>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>판정 점수</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>판정 경험치</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>요구 적성</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>요구 계정 Lv</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>eIndustryType</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n">
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n">
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="2" t="n"/>
+      <c r="J5" s="11" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n">
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n">
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -2120,222 +2334,222 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>IndustryLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>IndustryType</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>RequiredScore</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>ExpPerJudge</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>RequiredAptitude</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>RequiredAccountLevel</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
+      <c r="B9" s="7" t="n">
         <v>401</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>잡목림</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>30000</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
+      <c r="B10" s="7" t="n">
         <v>402</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>소나무 숲</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>90000</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
+      <c r="B11" s="7" t="n">
         <v>403</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>참나무 숲</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>270000</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
+      <c r="B12" s="7" t="n">
         <v>404</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>흑림</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>810000</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
+      <c r="B13" s="7" t="n">
         <v>405</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>세계수 뿌리</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="7" t="n">
         <v>2430000</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -2353,11 +2567,12 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2365,235 +2580,236 @@
   <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="1" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>산업 레벨 TID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>산업 종류</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>레벨</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>판정 1회 필요 점수 (적성1 = 1000점/초)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>판정 1회당 캐릭터 경험치</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>해금: 산업 적성 요구치</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>해금: 계정 레벨 요구치</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>설명 (메모 — 로직 미사용)</t>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>판정 점수</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>판정 경험치</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>요구 적성</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>요구 계정 Lv</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>eIndustryType</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n">
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n">
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="2" t="n"/>
+      <c r="J5" s="11" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n">
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n">
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -2601,222 +2817,222 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>IndustryLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>IndustryType</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>RequiredScore</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>ExpPerJudge</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>RequiredAptitude</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>RequiredAccountLevel</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
+      <c r="B9" s="7" t="n">
         <v>501</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>들판</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>30000</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
+      <c r="B10" s="7" t="n">
         <v>502</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>야산</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>90000</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
+      <c r="B11" s="7" t="n">
         <v>503</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>깊은 숲</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>270000</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
+      <c r="B12" s="7" t="n">
         <v>504</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>설산</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>810000</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
+      <c r="B13" s="7" t="n">
         <v>505</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>마수의 영역</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="7" t="n">
         <v>2430000</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -2834,5 +3050,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Industry.xlsx
+++ b/GameDesign/Excel/Industry.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,8 +47,22 @@
       <b val="1"/>
       <color theme="1"/>
     </font>
+    <font>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,8 +79,13 @@
         <fgColor theme="9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF79646"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -88,11 +107,12 @@
         <color indexed="64"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -129,6 +149,31 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -660,447 +705,463 @@
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="19" t="n"/>
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="19" t="n"/>
+      <c r="E1" s="19" t="n"/>
+      <c r="F1" s="19" t="n"/>
+      <c r="G1" s="19" t="n"/>
+      <c r="H1" s="19" t="n"/>
+      <c r="I1" s="19" t="n"/>
+      <c r="J1" s="19" t="n"/>
+    </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>산업 레벨 TID</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>산업 종류</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>레벨</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>판정 점수</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>판정 경험치</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>요구 적성</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>요구 계정 Lv</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>eIndustryType</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n">
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n">
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="11" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="11" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="A8" s="21" t="n"/>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>IndustryLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>IndustryType</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>RequiredScore</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>ExpPerJudge</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>RequiredAptitude</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>RequiredAccountLevel</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="7" t="n">
+      <c r="A9" s="19" t="n"/>
+      <c r="B9" s="17" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>텃밭</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="17" t="n">
         <v>30000</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="n">
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="17" t="n">
         <v>102</v>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>밭</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="17" t="n">
         <v>90000</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="7" t="n">
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="17" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>농장</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="17" t="n">
         <v>270000</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="n">
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="17" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>대농장</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="17" t="n">
         <v>810000</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="7" t="n">
+      <c r="A13" s="19" t="n"/>
+      <c r="B13" s="17" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>신성한 대지</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="17" t="n">
         <v>2430000</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="17" t="n">
         <v>81</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -1143,447 +1204,463 @@
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="19" t="n"/>
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="19" t="n"/>
+      <c r="E1" s="19" t="n"/>
+      <c r="F1" s="19" t="n"/>
+      <c r="G1" s="19" t="n"/>
+      <c r="H1" s="19" t="n"/>
+      <c r="I1" s="19" t="n"/>
+      <c r="J1" s="19" t="n"/>
+    </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>산업 레벨 TID</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>산업 종류</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>레벨</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>판정 점수</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>판정 경험치</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>요구 적성</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>요구 계정 Lv</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>eIndustryType</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n">
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n">
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="11" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="11" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="A8" s="21" t="n"/>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>IndustryLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>IndustryType</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>RequiredScore</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>ExpPerJudge</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>RequiredAptitude</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>RequiredAccountLevel</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="7" t="n">
+      <c r="A9" s="19" t="n"/>
+      <c r="B9" s="17" t="n">
         <v>201</v>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>개울</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="17" t="n">
         <v>30000</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="n">
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="17" t="n">
         <v>202</v>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>저수지</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="17" t="n">
         <v>90000</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="7" t="n">
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="17" t="n">
         <v>203</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>강 하류</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="17" t="n">
         <v>270000</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="n">
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="17" t="n">
         <v>204</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>호수</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="17" t="n">
         <v>810000</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="7" t="n">
+      <c r="A13" s="19" t="n"/>
+      <c r="B13" s="17" t="n">
         <v>205</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>심해</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="17" t="n">
         <v>2430000</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="17" t="n">
         <v>81</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -1626,447 +1703,463 @@
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="19" t="n"/>
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="19" t="n"/>
+      <c r="E1" s="19" t="n"/>
+      <c r="F1" s="19" t="n"/>
+      <c r="G1" s="19" t="n"/>
+      <c r="H1" s="19" t="n"/>
+      <c r="I1" s="19" t="n"/>
+      <c r="J1" s="19" t="n"/>
+    </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>산업 레벨 TID</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>산업 종류</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>레벨</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>판정 점수</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>판정 경험치</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>요구 적성</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>요구 계정 Lv</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>eIndustryType</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n">
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n">
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="11" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="11" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="A8" s="21" t="n"/>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>IndustryLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>IndustryType</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>RequiredScore</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>ExpPerJudge</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>RequiredAptitude</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>RequiredAccountLevel</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="7" t="n">
+      <c r="A9" s="19" t="n"/>
+      <c r="B9" s="17" t="n">
         <v>301</v>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>노천 광산</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="17" t="n">
         <v>30000</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="n">
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="17" t="n">
         <v>302</v>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>갱도</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="17" t="n">
         <v>90000</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="7" t="n">
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="17" t="n">
         <v>303</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>심층 갱도</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="17" t="n">
         <v>270000</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="n">
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="17" t="n">
         <v>304</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>지하 대공동</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="17" t="n">
         <v>810000</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="7" t="n">
+      <c r="A13" s="19" t="n"/>
+      <c r="B13" s="17" t="n">
         <v>305</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>심연</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="17" t="n">
         <v>2430000</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="17" t="n">
         <v>81</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -2109,447 +2202,463 @@
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="19" t="n"/>
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="19" t="n"/>
+      <c r="E1" s="19" t="n"/>
+      <c r="F1" s="19" t="n"/>
+      <c r="G1" s="19" t="n"/>
+      <c r="H1" s="19" t="n"/>
+      <c r="I1" s="19" t="n"/>
+      <c r="J1" s="19" t="n"/>
+    </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>산업 레벨 TID</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>산업 종류</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>레벨</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>판정 점수</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>판정 경험치</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>요구 적성</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>요구 계정 Lv</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>eIndustryType</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n">
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n">
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="11" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="11" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="A8" s="21" t="n"/>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>IndustryLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>IndustryType</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>RequiredScore</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>ExpPerJudge</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>RequiredAptitude</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>RequiredAccountLevel</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="7" t="n">
+      <c r="A9" s="19" t="n"/>
+      <c r="B9" s="17" t="n">
         <v>401</v>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>잡목림</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="17" t="n">
         <v>30000</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="n">
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="17" t="n">
         <v>402</v>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>소나무 숲</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="17" t="n">
         <v>90000</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="7" t="n">
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="17" t="n">
         <v>403</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>참나무 숲</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="17" t="n">
         <v>270000</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="n">
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="17" t="n">
         <v>404</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>흑림</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="17" t="n">
         <v>810000</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="7" t="n">
+      <c r="A13" s="19" t="n"/>
+      <c r="B13" s="17" t="n">
         <v>405</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>세계수 뿌리</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="17" t="n">
         <v>2430000</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="17" t="n">
         <v>81</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
@@ -2592,447 +2701,463 @@
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="19" t="n"/>
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="19" t="n"/>
+      <c r="E1" s="19" t="n"/>
+      <c r="F1" s="19" t="n"/>
+      <c r="G1" s="19" t="n"/>
+      <c r="H1" s="19" t="n"/>
+      <c r="I1" s="19" t="n"/>
+      <c r="J1" s="19" t="n"/>
+    </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>산업 레벨 TID</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>산업 종류</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>레벨</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>판정 점수</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>판정 경험치</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>요구 적성</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>요구 계정 Lv</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>eIndustryType</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n">
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n">
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="11" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="11" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="A8" s="21" t="n"/>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>IndustryLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>IndustryType</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>RequiredScore</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>ExpPerJudge</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>RequiredAptitude</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>RequiredAccountLevel</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="7" t="n">
+      <c r="A9" s="19" t="n"/>
+      <c r="B9" s="17" t="n">
         <v>501</v>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>들판</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="17" t="n">
         <v>30000</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="n">
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="17" t="n">
         <v>502</v>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>야산</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="17" t="n">
         <v>90000</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="7" t="n">
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="17" t="n">
         <v>503</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>깊은 숲</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="17" t="n">
         <v>270000</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="n">
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="17" t="n">
         <v>504</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>설산</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="17" t="n">
         <v>810000</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="7" t="n">
+      <c r="A13" s="19" t="n"/>
+      <c r="B13" s="17" t="n">
         <v>505</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>마수의 영역</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="17" t="n">
         <v>2430000</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="17" t="n">
         <v>81</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
         </is>

--- a/GameDesign/Excel/Industry.xlsx
+++ b/GameDesign/Excel/Industry.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -173,6 +173,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -272,11 +278,6 @@
         <t>해금: 산업 적성 요구치</t>
       </text>
     </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
-      <text>
-        <t>해금: 계정 레벨 요구치</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -300,11 +301,6 @@
     <comment ref="H2" authorId="0" shapeId="0">
       <text>
         <t>해금: 산업 적성 요구치</t>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
-      <text>
-        <t>해금: 계정 레벨 요구치</t>
       </text>
     </comment>
   </commentList>
@@ -332,11 +328,6 @@
         <t>해금: 산업 적성 요구치</t>
       </text>
     </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
-      <text>
-        <t>해금: 계정 레벨 요구치</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -362,11 +353,6 @@
         <t>해금: 산업 적성 요구치</t>
       </text>
     </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
-      <text>
-        <t>해금: 계정 레벨 요구치</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -390,11 +376,6 @@
     <comment ref="H2" authorId="0" shapeId="0">
       <text>
         <t>해금: 산업 적성 요구치</t>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
-      <text>
-        <t>해금: 계정 레벨 요구치</t>
       </text>
     </comment>
   </commentList>
@@ -690,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="2"/>
@@ -700,8 +681,8 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -715,7 +696,6 @@
       <c r="G1" s="19" t="n"/>
       <c r="H1" s="19" t="n"/>
       <c r="I1" s="19" t="n"/>
-      <c r="J1" s="19" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
@@ -755,15 +735,10 @@
       </c>
       <c r="H2" s="14" t="inlineStr">
         <is>
-          <t>요구 적성</t>
+          <t>해금 TID</t>
         </is>
       </c>
       <c r="I2" s="14" t="inlineStr">
-        <is>
-          <t>요구 계정 Lv</t>
-        </is>
-      </c>
-      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -815,11 +790,6 @@
           <t>a</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -863,11 +833,6 @@
         </is>
       </c>
       <c r="I4" s="15" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -894,10 +859,7 @@
       <c r="H5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -913,11 +875,8 @@
       <c r="E6" s="15" t="n"/>
       <c r="F6" s="15" t="n"/>
       <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
-        <v>10</v>
-      </c>
+      <c r="H6" s="15" t="n"/>
       <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
@@ -932,101 +891,78 @@
       <c r="F7" s="15" t="n"/>
       <c r="G7" s="15" t="n"/>
       <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="n"/>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n"/>
+      <c r="C8" s="23" t="n"/>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="23" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>UnlockTable.UnlockTID?</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>IndustryLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>IndustryType</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>RequiredScore</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>ExpPerJudge</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>RequiredAptitude</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>RequiredAccountLevel</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>UnlockTID</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="n"/>
-      <c r="B9" s="17" t="n">
-        <v>101</v>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>Farming</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>텃밭</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="n"/>
       <c r="B10" s="17" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
@@ -1034,35 +970,32 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>밭</t>
+          <t>텃밭</t>
         </is>
       </c>
       <c r="F10" s="17" t="n">
-        <v>90000</v>
+        <v>30000</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
+        <v>0</v>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="n"/>
       <c r="B11" s="17" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
@@ -1070,35 +1003,32 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>밭</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>90000</v>
+      </c>
+      <c r="G11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>농장</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>270000</v>
-      </c>
-      <c r="G11" s="17" t="n">
-        <v>9</v>
-      </c>
       <c r="H11" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="J11" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
+        <v>2102</v>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="n"/>
       <c r="B12" s="17" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
@@ -1106,64 +1036,91 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>대농장</t>
+          <t>농장</t>
         </is>
       </c>
       <c r="F12" s="17" t="n">
-        <v>810000</v>
+        <v>270000</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
+        <v>2103</v>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="n"/>
       <c r="B13" s="17" t="n">
+        <v>104</v>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>대농장</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>810000</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="17" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D14" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>신성한 대지</t>
         </is>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F14" s="17" t="n">
         <v>2430000</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G14" s="17" t="n">
         <v>81</v>
       </c>
-      <c r="H13" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>50</v>
-      </c>
-      <c r="J13" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
+      <c r="H14" s="17" t="n">
+        <v>2105</v>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="2"/>
@@ -1199,8 +1156,8 @@
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -1214,7 +1171,6 @@
       <c r="G1" s="19" t="n"/>
       <c r="H1" s="19" t="n"/>
       <c r="I1" s="19" t="n"/>
-      <c r="J1" s="19" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
@@ -1254,15 +1210,10 @@
       </c>
       <c r="H2" s="14" t="inlineStr">
         <is>
-          <t>요구 적성</t>
+          <t>해금 TID</t>
         </is>
       </c>
       <c r="I2" s="14" t="inlineStr">
-        <is>
-          <t>요구 계정 Lv</t>
-        </is>
-      </c>
-      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1314,11 +1265,6 @@
           <t>a</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -1362,11 +1308,6 @@
         </is>
       </c>
       <c r="I4" s="15" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1393,10 +1334,7 @@
       <c r="H5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -1412,11 +1350,8 @@
       <c r="E6" s="15" t="n"/>
       <c r="F6" s="15" t="n"/>
       <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
-        <v>10</v>
-      </c>
+      <c r="H6" s="15" t="n"/>
       <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
@@ -1431,101 +1366,78 @@
       <c r="F7" s="15" t="n"/>
       <c r="G7" s="15" t="n"/>
       <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="n"/>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n"/>
+      <c r="C8" s="23" t="n"/>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="23" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>UnlockTable.UnlockTID?</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>IndustryLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>IndustryType</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>RequiredScore</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>ExpPerJudge</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>RequiredAptitude</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>RequiredAccountLevel</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>UnlockTID</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="n"/>
-      <c r="B9" s="17" t="n">
-        <v>201</v>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>Fishing</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>개울</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="n"/>
       <c r="B10" s="17" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
@@ -1533,35 +1445,32 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>저수지</t>
+          <t>개울</t>
         </is>
       </c>
       <c r="F10" s="17" t="n">
-        <v>90000</v>
+        <v>30000</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
+        <v>0</v>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="n"/>
       <c r="B11" s="17" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
@@ -1569,35 +1478,32 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>저수지</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>90000</v>
+      </c>
+      <c r="G11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>강 하류</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>270000</v>
-      </c>
-      <c r="G11" s="17" t="n">
-        <v>9</v>
-      </c>
       <c r="H11" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="J11" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
+        <v>2202</v>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="n"/>
       <c r="B12" s="17" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
@@ -1605,64 +1511,91 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>호수</t>
+          <t>강 하류</t>
         </is>
       </c>
       <c r="F12" s="17" t="n">
-        <v>810000</v>
+        <v>270000</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
+        <v>2203</v>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="n"/>
       <c r="B13" s="17" t="n">
+        <v>204</v>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>호수</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>810000</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>2204</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="17" t="n">
         <v>205</v>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D14" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>심해</t>
         </is>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F14" s="17" t="n">
         <v>2430000</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G14" s="17" t="n">
         <v>81</v>
       </c>
-      <c r="H13" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>50</v>
-      </c>
-      <c r="J13" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
+      <c r="H14" s="17" t="n">
+        <v>2205</v>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="2"/>
@@ -1698,8 +1631,8 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -1713,7 +1646,6 @@
       <c r="G1" s="19" t="n"/>
       <c r="H1" s="19" t="n"/>
       <c r="I1" s="19" t="n"/>
-      <c r="J1" s="19" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
@@ -1753,15 +1685,10 @@
       </c>
       <c r="H2" s="14" t="inlineStr">
         <is>
-          <t>요구 적성</t>
+          <t>해금 TID</t>
         </is>
       </c>
       <c r="I2" s="14" t="inlineStr">
-        <is>
-          <t>요구 계정 Lv</t>
-        </is>
-      </c>
-      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1813,11 +1740,6 @@
           <t>a</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -1861,11 +1783,6 @@
         </is>
       </c>
       <c r="I4" s="15" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1892,10 +1809,7 @@
       <c r="H5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -1911,11 +1825,8 @@
       <c r="E6" s="15" t="n"/>
       <c r="F6" s="15" t="n"/>
       <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
-        <v>10</v>
-      </c>
+      <c r="H6" s="15" t="n"/>
       <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
@@ -1930,101 +1841,78 @@
       <c r="F7" s="15" t="n"/>
       <c r="G7" s="15" t="n"/>
       <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="n"/>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n"/>
+      <c r="C8" s="23" t="n"/>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="23" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>UnlockTable.UnlockTID?</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>IndustryLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>IndustryType</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>RequiredScore</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>ExpPerJudge</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>RequiredAptitude</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>RequiredAccountLevel</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>UnlockTID</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="n"/>
-      <c r="B9" s="17" t="n">
-        <v>301</v>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>Mining</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>노천 광산</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="n"/>
       <c r="B10" s="17" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
@@ -2032,35 +1920,32 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>갱도</t>
+          <t>노천 광산</t>
         </is>
       </c>
       <c r="F10" s="17" t="n">
-        <v>90000</v>
+        <v>30000</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
+        <v>0</v>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="n"/>
       <c r="B11" s="17" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
@@ -2068,35 +1953,32 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>갱도</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>90000</v>
+      </c>
+      <c r="G11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>심층 갱도</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>270000</v>
-      </c>
-      <c r="G11" s="17" t="n">
-        <v>9</v>
-      </c>
       <c r="H11" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="J11" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
+        <v>2302</v>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="n"/>
       <c r="B12" s="17" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
@@ -2104,64 +1986,91 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>지하 대공동</t>
+          <t>심층 갱도</t>
         </is>
       </c>
       <c r="F12" s="17" t="n">
-        <v>810000</v>
+        <v>270000</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
+        <v>2303</v>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="n"/>
       <c r="B13" s="17" t="n">
+        <v>304</v>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>지하 대공동</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>810000</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>2304</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="17" t="n">
         <v>305</v>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D14" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>심연</t>
         </is>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F14" s="17" t="n">
         <v>2430000</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G14" s="17" t="n">
         <v>81</v>
       </c>
-      <c r="H13" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>50</v>
-      </c>
-      <c r="J13" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
+      <c r="H14" s="17" t="n">
+        <v>2305</v>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="2"/>
@@ -2197,8 +2106,8 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -2212,7 +2121,6 @@
       <c r="G1" s="19" t="n"/>
       <c r="H1" s="19" t="n"/>
       <c r="I1" s="19" t="n"/>
-      <c r="J1" s="19" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
@@ -2252,15 +2160,10 @@
       </c>
       <c r="H2" s="14" t="inlineStr">
         <is>
-          <t>요구 적성</t>
+          <t>해금 TID</t>
         </is>
       </c>
       <c r="I2" s="14" t="inlineStr">
-        <is>
-          <t>요구 계정 Lv</t>
-        </is>
-      </c>
-      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -2312,11 +2215,6 @@
           <t>a</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -2360,11 +2258,6 @@
         </is>
       </c>
       <c r="I4" s="15" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -2391,10 +2284,7 @@
       <c r="H5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -2410,11 +2300,8 @@
       <c r="E6" s="15" t="n"/>
       <c r="F6" s="15" t="n"/>
       <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
-        <v>10</v>
-      </c>
+      <c r="H6" s="15" t="n"/>
       <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
@@ -2429,101 +2316,78 @@
       <c r="F7" s="15" t="n"/>
       <c r="G7" s="15" t="n"/>
       <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="n"/>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n"/>
+      <c r="C8" s="23" t="n"/>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="23" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>UnlockTable.UnlockTID?</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>IndustryLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>IndustryType</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>RequiredScore</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>ExpPerJudge</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>RequiredAptitude</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>RequiredAccountLevel</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>UnlockTID</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="n"/>
-      <c r="B9" s="17" t="n">
-        <v>401</v>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>Logging</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>잡목림</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="n"/>
       <c r="B10" s="17" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
@@ -2531,35 +2395,32 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>소나무 숲</t>
+          <t>잡목림</t>
         </is>
       </c>
       <c r="F10" s="17" t="n">
-        <v>90000</v>
+        <v>30000</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
+        <v>0</v>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="n"/>
       <c r="B11" s="17" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
@@ -2567,35 +2428,32 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>소나무 숲</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>90000</v>
+      </c>
+      <c r="G11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>참나무 숲</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>270000</v>
-      </c>
-      <c r="G11" s="17" t="n">
-        <v>9</v>
-      </c>
       <c r="H11" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="J11" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
+        <v>2402</v>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="n"/>
       <c r="B12" s="17" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
@@ -2603,64 +2461,91 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>흑림</t>
+          <t>참나무 숲</t>
         </is>
       </c>
       <c r="F12" s="17" t="n">
-        <v>810000</v>
+        <v>270000</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
+        <v>2403</v>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="n"/>
       <c r="B13" s="17" t="n">
+        <v>404</v>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>흑림</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>810000</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>2404</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="17" t="n">
         <v>405</v>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D14" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>세계수 뿌리</t>
         </is>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F14" s="17" t="n">
         <v>2430000</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G14" s="17" t="n">
         <v>81</v>
       </c>
-      <c r="H13" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>50</v>
-      </c>
-      <c r="J13" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
+      <c r="H14" s="17" t="n">
+        <v>2405</v>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="2"/>
@@ -2696,8 +2581,8 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -2711,7 +2596,6 @@
       <c r="G1" s="19" t="n"/>
       <c r="H1" s="19" t="n"/>
       <c r="I1" s="19" t="n"/>
-      <c r="J1" s="19" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
@@ -2751,15 +2635,10 @@
       </c>
       <c r="H2" s="14" t="inlineStr">
         <is>
-          <t>요구 적성</t>
+          <t>해금 TID</t>
         </is>
       </c>
       <c r="I2" s="14" t="inlineStr">
-        <is>
-          <t>요구 계정 Lv</t>
-        </is>
-      </c>
-      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -2811,11 +2690,6 @@
           <t>a</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -2859,11 +2733,6 @@
         </is>
       </c>
       <c r="I4" s="15" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -2890,10 +2759,7 @@
       <c r="H5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -2909,11 +2775,8 @@
       <c r="E6" s="15" t="n"/>
       <c r="F6" s="15" t="n"/>
       <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
-        <v>10</v>
-      </c>
+      <c r="H6" s="15" t="n"/>
       <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
@@ -2928,101 +2791,78 @@
       <c r="F7" s="15" t="n"/>
       <c r="G7" s="15" t="n"/>
       <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="n"/>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n"/>
+      <c r="C8" s="23" t="n"/>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="23" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>UnlockTable.UnlockTID?</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>IndustryLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>IndustryType</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>RequiredScore</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>ExpPerJudge</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>RequiredAptitude</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>RequiredAccountLevel</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>UnlockTID</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="n"/>
-      <c r="B9" s="17" t="n">
-        <v>501</v>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>Hunting</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>들판</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="n"/>
       <c r="B10" s="17" t="n">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
@@ -3030,35 +2870,32 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>야산</t>
+          <t>들판</t>
         </is>
       </c>
       <c r="F10" s="17" t="n">
-        <v>90000</v>
+        <v>30000</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초 · 해금 요구치는 임시값(T-016)</t>
+        <v>0</v>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 30초 / 적성10 7.5초</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="n"/>
       <c r="B11" s="17" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
@@ -3066,35 +2903,32 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>야산</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>90000</v>
+      </c>
+      <c r="G11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>깊은 숲</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>270000</v>
-      </c>
-      <c r="G11" s="17" t="n">
-        <v>9</v>
-      </c>
       <c r="H11" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="J11" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초 · 해금 요구치는 임시값(T-016)</t>
+        <v>2502</v>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 1분 30초 / 적성10 22.5초</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="n"/>
       <c r="B12" s="17" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
@@ -3102,64 +2936,91 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>설산</t>
+          <t>깊은 숲</t>
         </is>
       </c>
       <c r="F12" s="17" t="n">
-        <v>810000</v>
+        <v>270000</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초 · 해금 요구치는 임시값(T-016)</t>
+        <v>2503</v>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 4분 30초 / 적성10 1분 7.5초</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="n"/>
       <c r="B13" s="17" t="n">
+        <v>504</v>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>설산</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>810000</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>2504</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 13분 30초 / 적성10 3분 22.5초</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="17" t="n">
         <v>505</v>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D14" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>마수의 영역</t>
         </is>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F14" s="17" t="n">
         <v>2430000</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G14" s="17" t="n">
         <v>81</v>
       </c>
-      <c r="H13" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>50</v>
-      </c>
-      <c r="J13" s="18" t="inlineStr">
-        <is>
-          <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초 · 해금 요구치는 임시값(T-016)</t>
+      <c r="H14" s="17" t="n">
+        <v>2505</v>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>판정 1회 — 적성1 40분 30초 / 적성10 10분 7.5초</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/Industry.xlsx
+++ b/GameDesign/Excel/Industry.xlsx
@@ -666,7 +666,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1017,7 +1017,7 @@
         <v>3</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>2102</v>
+        <v>0</v>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>9</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>2103</v>
+        <v>0</v>
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>27</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>2104</v>
+        <v>0</v>
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>81</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>2105</v>
+        <v>0</v>
       </c>
       <c r="I14" s="18" t="inlineStr">
         <is>
@@ -1136,12 +1136,12 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1492,7 +1492,7 @@
         <v>3</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>2202</v>
+        <v>0</v>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>9</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>2203</v>
+        <v>0</v>
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>27</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>2204</v>
+        <v>0</v>
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>81</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>2205</v>
+        <v>0</v>
       </c>
       <c r="I14" s="18" t="inlineStr">
         <is>
@@ -1611,12 +1611,12 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1967,7 +1967,7 @@
         <v>3</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>2302</v>
+        <v>0</v>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>9</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>2303</v>
+        <v>0</v>
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>27</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>2304</v>
+        <v>0</v>
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>81</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>2305</v>
+        <v>0</v>
       </c>
       <c r="I14" s="18" t="inlineStr">
         <is>
@@ -2086,12 +2086,12 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2442,7 +2442,7 @@
         <v>3</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>2402</v>
+        <v>0</v>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>9</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>2403</v>
+        <v>0</v>
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>27</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>2404</v>
+        <v>0</v>
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>81</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>2405</v>
+        <v>0</v>
       </c>
       <c r="I14" s="18" t="inlineStr">
         <is>
@@ -2561,12 +2561,12 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2917,7 +2917,7 @@
         <v>3</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>2502</v>
+        <v>0</v>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>9</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>2503</v>
+        <v>0</v>
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>27</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>2504</v>
+        <v>0</v>
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>81</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>2505</v>
+        <v>0</v>
       </c>
       <c r="I14" s="18" t="inlineStr">
         <is>
@@ -3036,6 +3036,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Industry.xlsx
+++ b/GameDesign/Excel/Industry.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="IndustryLevelTable.농사" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="IndustryLevelTable.낚시" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="IndustryLevelTable.발굴" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="IndustryLevelTable.채굴" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="IndustryLevelTable.벌목" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="IndustryLevelTable.사냥" sheetId="5" state="visible" r:id="rId5"/>
@@ -1153,7 +1153,7 @@
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="D10" s="17" t="n">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>개울</t>
+          <t>옛 집터</t>
         </is>
       </c>
       <c r="F10" s="17" t="n">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="E11" s="18" t="inlineStr">
         <is>
-          <t>저수지</t>
+          <t>무너진 성벽</t>
         </is>
       </c>
       <c r="F11" s="17" t="n">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="D12" s="17" t="n">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>강 하류</t>
+          <t>고대 신전</t>
         </is>
       </c>
       <c r="F12" s="17" t="n">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>호수</t>
+          <t>지하 묘실</t>
         </is>
       </c>
       <c r="F13" s="17" t="n">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="D14" s="17" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="E14" s="18" t="inlineStr">
         <is>
-          <t>심해</t>
+          <t>잊힌 왕도</t>
         </is>
       </c>
       <c r="F14" s="17" t="n">

--- a/GameDesign/Excel/Industry.xlsx
+++ b/GameDesign/Excel/Industry.xlsx
@@ -666,7 +666,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -814,7 +814,7 @@
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
       <c r="F4" s="15" t="inlineStr">
@@ -1136,12 +1136,12 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
       <c r="F4" s="15" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
       <c r="F4" s="15" t="inlineStr">
@@ -2086,12 +2086,12 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
       <c r="F4" s="15" t="inlineStr">
@@ -2561,12 +2561,12 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
       <c r="F4" s="15" t="inlineStr">
@@ -3036,6 +3036,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>